--- a/data/trans_camb/P1419-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1419-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,9</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,6</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,62</t>
+          <t>-2,77; 0,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,2</t>
+          <t>-2,86; 0,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,19</t>
+          <t>-0,62; 3,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 4,04</t>
+          <t>-2,05; 3,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; -0,68</t>
+          <t>-5,75; -0,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,63</t>
+          <t>0,7; 6,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,73</t>
+          <t>-1,85; 1,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -0,85</t>
+          <t>-3,85; -0,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,36</t>
+          <t>0,76; 4,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,6; 46,62</t>
+          <t>-76,09; 45,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 20,36</t>
+          <t>-78,85; 15,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 175,77</t>
+          <t>-24,51; 174,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 65,59</t>
+          <t>-23,3; 55,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,79; -8,95</t>
+          <t>-64,34; -9,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 103,22</t>
+          <t>6,4; 104,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 38,24</t>
+          <t>-30,04; 36,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,23; -17,69</t>
+          <t>-61,97; -15,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 95,68</t>
+          <t>11,62; 94,02</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,22 +865,22 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-2,72</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>-0,02</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-2,72</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,52</t>
+          <t>-3,24; -0,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,78</t>
+          <t>-3,19; -0,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,91</t>
+          <t>-1,34; 1,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 0,89</t>
+          <t>-4,79; 0,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -0,82</t>
+          <t>-6,27; -0,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,48</t>
+          <t>-2,83; 2,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -0,22</t>
+          <t>-3,29; -0,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -1,23</t>
+          <t>-4,23; -1,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,75</t>
+          <t>-1,46; 1,58</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-19,95%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0,14%</t>
+          <t>-1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-11,3%</t>
+          <t>-0,35%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,99; -20,57</t>
+          <t>-83,93; -20,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,65; -35,78</t>
+          <t>-87,03; -27,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,44; 41,3</t>
+          <t>-36,79; 84,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 9,15</t>
+          <t>-38,87; 8,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,71; -7,72</t>
+          <t>-49,25; -3,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 26,54</t>
+          <t>-22,45; 25,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,49; -2,83</t>
+          <t>-42,35; -3,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,99; -20,03</t>
+          <t>-55,27; -18,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-43,78; 11,51</t>
+          <t>-18,46; 27,88</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,02</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; -0,7</t>
+          <t>-4,07; -0,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,27</t>
+          <t>-3,69; -0,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,93</t>
+          <t>-0,91; 3,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -0,77</t>
+          <t>-6,86; -0,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -4,56</t>
+          <t>-10,14; -4,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 0,54</t>
+          <t>-3,12; 2,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -1,0</t>
+          <t>-4,67; -1,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -2,9</t>
+          <t>-6,18; -2,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,18</t>
+          <t>-1,27; 2,49</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-26,26%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,78%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-88,39; -22,3</t>
+          <t>-89,34; -18,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,18; -5,41</t>
+          <t>-78,26; 3,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 130,36</t>
+          <t>-22,58; 143,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,46; -6,02</t>
+          <t>-51,98; -3,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,84; -45,07</t>
+          <t>-75,92; -44,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 4,44</t>
+          <t>-23,03; 30,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,09; -14,74</t>
+          <t>-54,81; -17,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,25; -43,81</t>
+          <t>-72,94; -43,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 17,51</t>
+          <t>-14,77; 38,45</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,64</t>
+          <t>-1,99</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,89</t>
+          <t>-3,49; -0,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,82</t>
+          <t>-2,2; 0,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,68</t>
+          <t>-0,72; 2,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; -1,76</t>
+          <t>-6,86; -1,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,57; -2,42</t>
+          <t>-7,54; -2,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,03</t>
+          <t>-4,8; 0,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,83; -1,63</t>
+          <t>-4,82; -1,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -1,35</t>
+          <t>-4,54; -1,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,78</t>
+          <t>-2,16; 0,79</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-21,75%</t>
+          <t>-16,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-10,09%</t>
+          <t>-7,35%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-85,37; -22,85</t>
+          <t>-84,87; -27,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,86; 34,86</t>
+          <t>-56,93; 36,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 109,31</t>
+          <t>-18,37; 101,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,01; -15,67</t>
+          <t>-50,3; -15,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,39; -21,74</t>
+          <t>-54,97; -19,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,76; -0,67</t>
+          <t>-34,88; 4,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-54,34; -22,84</t>
+          <t>-54,8; -24,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,83; -19,34</t>
+          <t>-51,67; -17,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 11,35</t>
+          <t>-24,63; 11,25</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -1,15</t>
+          <t>-2,59; -1,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; -0,78</t>
+          <t>-2,23; -0,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,4</t>
+          <t>-0,08; 1,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,93</t>
+          <t>-3,76; -1,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -3,19</t>
+          <t>-6,07; -3,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,67</t>
+          <t>-1,22; 1,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -1,25</t>
+          <t>-2,84; -1,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -2,34</t>
+          <t>-3,86; -2,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,86</t>
+          <t>-0,36; 1,4</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-7,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,45%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-73,17; -40,89</t>
+          <t>-73,59; -41,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-65,38; -30,11</t>
+          <t>-64,25; -28,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 53,62</t>
+          <t>-2,19; 63,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,04; -9,15</t>
+          <t>-32,33; -10,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,16; -31,78</t>
+          <t>-52,62; -32,44</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 6,52</t>
+          <t>-10,55; 15,49</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,05; -18,9</t>
+          <t>-39,02; -19,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,73; -34,87</t>
+          <t>-51,78; -34,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 13,3</t>
+          <t>-4,72; 22,54</t>
         </is>
       </c>
     </row>
